--- a/tests/SafeOpenXml.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra06e99399daa474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb1e3a8b4a04479e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4c893d43b9a472f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Refac1ee787be419b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f30d395e67544fd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R922daed12f894e94"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcb1e3a8b4a04479e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ee5d3d46c264fe2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Refac1ee787be419b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6e5b85c226194725"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R922daed12f894e94"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b820efed50a4966"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ee5d3d46c264fe2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83eb901961c943a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6e5b85c226194725"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd7b8d7e644b14243"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b820efed50a4966"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e9a63be376b4ea8"/>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83eb901961c943a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf0364d16f9e5426d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd7b8d7e644b14243"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd77acec5a1814a76"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e9a63be376b4ea8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c8d9ad2369b40b0"/>
 </x:worksheet>
 </file>